--- a/artfynd/A 32216-2023 artfynd.xlsx
+++ b/artfynd/A 32216-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115429720</v>
+        <v>115429501</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590294</v>
+        <v>590301</v>
       </c>
       <c r="R2" t="n">
-        <v>7006755</v>
+        <v>7006778</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -770,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115429725</v>
+        <v>115429502</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590309</v>
+        <v>590324</v>
       </c>
       <c r="R3" t="n">
-        <v>7006834</v>
+        <v>7006800</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -877,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115429726</v>
+        <v>115429503</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590321</v>
+        <v>590309</v>
       </c>
       <c r="R4" t="n">
-        <v>7006833</v>
+        <v>7006831</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115429723</v>
+        <v>115429477</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590293</v>
+        <v>590308</v>
       </c>
       <c r="R5" t="n">
-        <v>7006790</v>
+        <v>7006785</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115429479</v>
+        <v>115429478</v>
       </c>
       <c r="B6" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590302</v>
+        <v>590348</v>
       </c>
       <c r="R6" t="n">
-        <v>7006823</v>
+        <v>7006782</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1205,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115429505</v>
+        <v>115429479</v>
       </c>
       <c r="B7" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590438</v>
+        <v>590302</v>
       </c>
       <c r="R7" t="n">
-        <v>7006876</v>
+        <v>7006823</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1307,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115429719</v>
+        <v>115429481</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,39 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590298</v>
+        <v>590380</v>
       </c>
       <c r="R8" t="n">
-        <v>7006735</v>
+        <v>7006919</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1402,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115429502</v>
+        <v>115429498</v>
       </c>
       <c r="B9" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590324</v>
+        <v>590301</v>
       </c>
       <c r="R9" t="n">
-        <v>7006800</v>
+        <v>7006778</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1516,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115429722</v>
+        <v>115429505</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,39 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590283</v>
+        <v>590438</v>
       </c>
       <c r="R10" t="n">
-        <v>7006785</v>
+        <v>7006876</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1611,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115429724</v>
+        <v>115429483</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590295</v>
+        <v>590436</v>
       </c>
       <c r="R11" t="n">
-        <v>7006796</v>
+        <v>7006832</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1718,27 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115429489</v>
+        <v>115429488</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590340</v>
+        <v>590333</v>
       </c>
       <c r="R12" t="n">
-        <v>7006865</v>
+        <v>7006679</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1837,50 +1752,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115429498</v>
+        <v>115429489</v>
       </c>
       <c r="B13" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590301</v>
+        <v>590340</v>
       </c>
       <c r="R13" t="n">
-        <v>7006778</v>
+        <v>7006865</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1939,15 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115429478</v>
+        <v>115429490</v>
       </c>
       <c r="B14" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,34 +1865,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590348</v>
+        <v>590358</v>
       </c>
       <c r="R14" t="n">
-        <v>7006782</v>
+        <v>7006934</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2041,15 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115429501</v>
+        <v>115429713</v>
       </c>
       <c r="B15" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,34 +1967,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590301</v>
+        <v>590400</v>
       </c>
       <c r="R15" t="n">
-        <v>7006778</v>
+        <v>7006771</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2131,27 +2046,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115429718</v>
+        <v>115429715</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590305</v>
+        <v>590340</v>
       </c>
       <c r="R16" t="n">
-        <v>7006715</v>
+        <v>7006693</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2250,15 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115429503</v>
+        <v>115429716</v>
       </c>
       <c r="B17" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,34 +2171,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590309</v>
+        <v>590337</v>
       </c>
       <c r="R17" t="n">
-        <v>7006831</v>
+        <v>7006699</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2340,27 +2250,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115429721</v>
+        <v>115429717</v>
       </c>
       <c r="B18" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590292</v>
+        <v>590320</v>
       </c>
       <c r="R18" t="n">
-        <v>7006743</v>
+        <v>7006700</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2459,15 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115429717</v>
+        <v>115429718</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590320</v>
+        <v>590305</v>
       </c>
       <c r="R19" t="n">
-        <v>7006700</v>
+        <v>7006715</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2566,15 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115429477</v>
+        <v>115429719</v>
       </c>
       <c r="B20" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,34 +2477,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590308</v>
+        <v>590298</v>
       </c>
       <c r="R20" t="n">
-        <v>7006785</v>
+        <v>7006735</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2656,15 +2556,831 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115429720</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>590294</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7006755</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115429721</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>590292</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7006743</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115429722</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>590283</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7006785</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>115429723</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>590293</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7006790</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>115429724</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>590295</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7006796</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115429725</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>590309</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7006834</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>115429726</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>590321</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7006833</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115429731</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>590386</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7006937</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32216-2023 artfynd.xlsx
+++ b/artfynd/A 32216-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429502</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429477</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429478</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429479</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429498</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429505</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429483</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429488</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429489</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429490</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429713</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429716</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429717</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429718</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429719</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2667,6 +2767,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429720</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429721</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429722</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2973,6 +3088,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429723</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3075,6 +3195,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429724</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3177,6 +3302,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429725</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3279,6 +3409,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429726</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3381,8 +3516,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429731</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>